--- a/CHARMS LOCKET.xlsx
+++ b/CHARMS LOCKET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87553FBF-38E6-4B2F-AD7C-5C3937D79D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C13B73-38C6-4286-9E06-38F2F2FEA787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E6A8523F-E3AD-47A2-8921-8093ECE4490C}"/>
   </bookViews>
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,6 +223,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4026,7 +4038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77653718-B859-464F-A06A-1D56430E57AB}">
-  <dimension ref="A1:K757"/>
+  <dimension ref="A1:K573"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
@@ -4336,9 +4348,7 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I11" s="10">
-        <v>2</v>
-      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
@@ -4367,9 +4377,7 @@
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>1</v>
-      </c>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
@@ -4448,9 +4456,7 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
     </row>
@@ -6237,25 +6243,25 @@
       <c r="K81" s="10"/>
     </row>
     <row r="82" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6">
+      <c r="A82" s="12">
         <v>1</v>
       </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="8">
-        <v>3.68</v>
-      </c>
-      <c r="D82" s="9">
+      <c r="B82" s="13"/>
+      <c r="C82" s="14">
+        <v>3.68</v>
+      </c>
+      <c r="D82" s="15">
         <f t="shared" si="3"/>
         <v>32.44</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="15">
         <f t="shared" si="4"/>
         <v>64.88</v>
       </c>
-      <c r="F82" s="9">
-        <v>65</v>
-      </c>
-      <c r="G82" s="9">
+      <c r="F82" s="15">
+        <v>65</v>
+      </c>
+      <c r="G82" s="15">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
@@ -6263,681 +6269,497 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
     </row>
-    <row r="83" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
